--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2021_valparaiso.xlsx
@@ -870,7 +870,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:30</t>
+    <t xml:space="preserve">2026-09-18 14:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_migracion_flujos_od_2021_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_migracion_flujos_od_2021_valparaiso.xlsx
@@ -870,7 +870,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:10</t>
+    <t xml:space="preserve">2026-10-05 04:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
